--- a/hardware/pcb_1/bom/pcb_1-bom.xlsx
+++ b/hardware/pcb_1/bom/pcb_1-bom.xlsx
@@ -113,7 +113,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-04-03_12-45-31</t>
+    <t>2026-04-03_12-51-30</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/hardware/pcb_1/bom/pcb_1-bom.xlsx
+++ b/hardware/pcb_1/bom/pcb_1-bom.xlsx
@@ -113,7 +113,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-04-03_12-51-30</t>
+    <t>2026-04-03_12-56-35</t>
   </si>
   <si>
     <t>KiCad Version:</t>

--- a/hardware/pcb_1/bom/pcb_1-bom.xlsx
+++ b/hardware/pcb_1/bom/pcb_1-bom.xlsx
@@ -113,7 +113,7 @@
     <t>Date:</t>
   </si>
   <si>
-    <t>2026-04-03_12-56-35</t>
+    <t>2026-04-03_13-13-15</t>
   </si>
   <si>
     <t>KiCad Version:</t>
